--- a/analysis/output_bge-m3/A1_ai_review.xlsx
+++ b/analysis/output_bge-m3/A1_ai_review.xlsx
@@ -653,12 +653,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>H. 경영역량 강화·사업화 지원(컨설팅·마케팅·디자인)</t>
+          <t>G. 경영역량 강화·사업화 지원(컨설팅·마케팅·디자인)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>H1 컨설팅·교육·마케팅 지원</t>
+          <t>G1 경영역량 강화·판로 확대(컨설팅·교육·마케팅)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>H. 경영역량 강화·사업화 지원(컨설팅·마케팅·디자인)</t>
+          <t>G. 경영역량 강화·사업화 지원(컨설팅·마케팅·디자인)</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>H1 컨설팅·교육·마케팅 지원</t>
+          <t>G1 경영역량 강화·판로 확대(컨설팅·교육·마케팅)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>F. 전문인력 양성·채용 지원</t>
+          <t>F. 인력 양성·고용 지원(전문인력·직업훈련·고용장려·노동환경)</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>F. 전문인력 양성·채용 지원</t>
+          <t>F. 인력 양성·고용 지원(전문인력·직업훈련·고용장려·노동환경)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>D1 정책자금 융자(운전·시설자금)</t>
+          <t>D1 운전·시설자금 조달 지원(정책자금 융자)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>F. 전문인력 양성·채용 지원</t>
+          <t>F. 인력 양성·고용 지원(전문인력·직업훈련·고용장려·노동환경)</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>G. 고용 창출·유지 및 노동환경 개선</t>
+          <t>F. 인력 양성·고용 지원(전문인력·직업훈련·고용장려·노동환경)</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>G3 재직자·사업주 직업훈련 지원</t>
+          <t>F2 재직자·사업주 직업훈련 지원</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>G. 고용 창출·유지 및 노동환경 개선</t>
+          <t>F. 인력 양성·고용 지원(전문인력·직업훈련·고용장려·노동환경)</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>G3 재직자·사업주 직업훈련 지원</t>
+          <t>F2 재직자·사업주 직업훈련 지원</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>H. 경영역량 강화·사업화 지원(컨설팅·마케팅·디자인)</t>
+          <t>G. 경영역량 강화·사업화 지원(컨설팅·마케팅·디자인)</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>H1 컨설팅·교육·마케팅 지원</t>
+          <t>G1 경영역량 강화·판로 확대(컨설팅·교육·마케팅)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>H. 경영역량 강화·사업화 지원(컨설팅·마케팅·디자인)</t>
+          <t>G. 경영역량 강화·사업화 지원(컨설팅·마케팅·디자인)</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>H1 컨설팅·교육·마케팅 지원</t>
+          <t>G1 경영역량 강화·판로 확대(컨설팅·교육·마케팅)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>G. 고용 창출·유지 및 노동환경 개선</t>
+          <t>F. 인력 양성·고용 지원(전문인력·직업훈련·고용장려·노동환경)</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>G3 재직자·사업주 직업훈련 지원</t>
+          <t>F2 재직자·사업주 직업훈련 지원</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>F. 전문인력 양성·채용 지원</t>
+          <t>F. 인력 양성·고용 지원(전문인력·직업훈련·고용장려·노동환경)</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>F. 전문인력 양성·채용 지원</t>
+          <t>F. 인력 양성·고용 지원(전문인력·직업훈련·고용장려·노동환경)</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>F. 전문인력 양성·채용 지원</t>
+          <t>F. 인력 양성·고용 지원(전문인력·직업훈련·고용장려·노동환경)</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>F. 전문인력 양성·채용 지원</t>
+          <t>F. 인력 양성·고용 지원(전문인력·직업훈련·고용장려·노동환경)</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>F. 전문인력 양성·채용 지원</t>
+          <t>F. 인력 양성·고용 지원(전문인력·직업훈련·고용장려·노동환경)</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>F. 전문인력 양성·채용 지원</t>
+          <t>F. 인력 양성·고용 지원(전문인력·직업훈련·고용장려·노동환경)</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>D1 정책자금 융자(운전·시설자금)</t>
+          <t>D1 운전·시설자금 조달 지원(정책자금 융자)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>F. 전문인력 양성·채용 지원</t>
+          <t>F. 인력 양성·고용 지원(전문인력·직업훈련·고용장려·노동환경)</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>D1 정책자금 융자(운전·시설자금)</t>
+          <t>D1 운전·시설자금 조달 지원(정책자금 융자)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>F. 전문인력 양성·채용 지원</t>
+          <t>F. 인력 양성·고용 지원(전문인력·직업훈련·고용장려·노동환경)</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
